--- a/DATOS/Datos procesados/Geolocalización Vicente López - Unificado.xlsx
+++ b/DATOS/Datos procesados/Geolocalización Vicente López - Unificado.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5fa8a9efe53b17c/Documentos/TP FINAL DATOS/DATOS/Datos procesados/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_04543DCC8D2447A277DA07692C918A9B6C38E299" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F752E321-22E1-4C24-BD42-F484291936E5}"/>
+  <bookViews>
+    <workbookView xWindow="5280" yWindow="1368" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -844,21 +853,22 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -868,11 +878,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -886,45 +902,40 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1114,17 +1125,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E68"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1141,7 +1158,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1158,7 +1175,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1175,7 +1192,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1192,7 +1209,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1209,7 +1226,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -1226,7 +1243,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
@@ -1243,7 +1260,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
@@ -1260,7 +1277,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
@@ -1277,7 +1294,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
@@ -1294,7 +1311,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
@@ -1311,7 +1328,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>45</v>
       </c>
@@ -1328,7 +1345,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -1345,7 +1362,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
@@ -1362,7 +1379,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>57</v>
       </c>
@@ -1379,908 +1396,908 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>94</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>113</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="s">
+    <row r="38" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>153</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="2" t="s">
         <v>156</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>162</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="2" t="s">
         <v>164</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>166</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>170</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>174</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="2" t="s">
         <v>176</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>178</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="s">
+    <row r="46" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
         <v>182</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="s">
+    <row r="47" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>187</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="2" t="s">
         <v>189</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="s">
+    <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>191</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="2" t="s">
         <v>193</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="s">
+    <row r="49" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="2" t="s">
         <v>197</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="s">
+    <row r="50" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>199</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="2" t="s">
         <v>201</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="s">
+    <row r="51" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>203</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="2" t="s">
         <v>205</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="s">
+    <row r="52" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
         <v>207</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="2" t="s">
         <v>209</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="s">
+    <row r="53" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>211</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="2" t="s">
         <v>214</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="s">
+    <row r="54" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="2" t="s">
         <v>218</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="s">
+    <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>220</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="2" t="s">
         <v>222</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="s">
+    <row r="56" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>224</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="2" t="s">
         <v>226</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="s">
+    <row r="57" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>228</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="2" t="s">
         <v>230</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4" t="s">
+    <row r="58" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
         <v>232</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="2" t="s">
         <v>234</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="s">
+    <row r="59" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="2" t="s">
         <v>238</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="s">
+    <row r="60" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
         <v>240</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="2" t="s">
         <v>242</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="s">
+    <row r="61" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
         <v>244</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="2" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="s">
+    <row r="62" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
         <v>248</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="s">
+    <row r="63" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>252</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="s">
+    <row r="64" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>256</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="s">
+    <row r="65" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>260</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="s">
+    <row r="66" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>264</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="2" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="s">
+    <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
         <v>268</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="2" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="s">
+    <row r="68" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>272</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E68" s="2" t="s">
         <v>275</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>